--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satyam.CLOUDYCOOL\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F718507-A5C6-4DDD-864B-B1046B36CFDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4665E14-9296-465B-A7EF-B8144438D411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B5181292-B819-4253-93D6-A2C77ED0862A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
   <si>
     <t xml:space="preserve">Project Name </t>
   </si>
@@ -108,6 +108,15 @@
   </si>
   <si>
     <t>Build a Rewst workflow that enables Continuous technicians to adjust Pax8 license quantities directly, simplifying the change process and reducing errors.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teams Notification </t>
+  </si>
+  <si>
+    <t>Graph, HaloPSA, Rewst</t>
+  </si>
+  <si>
+    <t>Developed a Microsoft Teams notification system that posts updates to a Teams channel, tagging relevant users when tickets are updated upon workflow completion. Currently implemented for onboarding and offboarding processes, with flexibility to be reused as a sub-workflow or completion handler for future automations.</t>
   </si>
 </sst>
 </file>
@@ -498,7 +507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D3FE286-6749-4234-BE82-DEFA19428F78}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27" style="2" bestFit="1" customWidth="1"/>
@@ -603,7 +612,21 @@
         <v>19</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -616,23 +639,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="9cb81d7b-fefe-42a9-a0f2-5871603dfeb9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010037CFE03F1E3D084DA4C7DCDB2F33373B" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="48fbfec5ba6da941d58a6bba8473d12a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="9cb81d7b-fefe-42a9-a0f2-5871603dfeb9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0e0a672e89e325df77fa989dac01fde5" ns3:_="">
     <xsd:import namespace="9cb81d7b-fefe-42a9-a0f2-5871603dfeb9"/>
@@ -782,31 +788,24 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="9cb81d7b-fefe-42a9-a0f2-5871603dfeb9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F975563D-C219-4A29-B1CB-37D50519E395}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="9cb81d7b-fefe-42a9-a0f2-5871603dfeb9"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8188391C-85BF-4856-861E-1F470AB9C963}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B78AE0C9-394B-4984-AE8D-B785F12488C7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -822,4 +821,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8188391C-85BF-4856-861E-1F470AB9C963}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F975563D-C219-4A29-B1CB-37D50519E395}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="9cb81d7b-fefe-42a9-a0f2-5871603dfeb9"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satyam.CLOUDYCOOL\Desktop\Dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://continuousnet-my.sharepoint.com/personal/satyam_continuous_net/Documents/Desktop/Project Tracker Dashboard/project-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4665E14-9296-465B-A7EF-B8144438D411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{C4665E14-9296-465B-A7EF-B8144438D411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E801EA7F-8186-4A6D-8878-10ED36AC1666}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B5181292-B819-4253-93D6-A2C77ED0862A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
   <si>
     <t xml:space="preserve">Project Name </t>
   </si>
@@ -86,9 +86,6 @@
     <t>Rewst, MS365, HaloPSA, Perimeter81</t>
   </si>
   <si>
-    <t>This project is centered on streamlining the user onboarding process, including updating and optimizing forms and workflows, troubleshooting and resolving workflow issues, and ensuring proper documentation and response management via support tickets.</t>
-  </si>
-  <si>
     <t>Rewst, MS365, Perimeter81, HaloPSA</t>
   </si>
   <si>
@@ -117,6 +114,24 @@
   </si>
   <si>
     <t>Developed a Microsoft Teams notification system that posts updates to a Teams channel, tagging relevant users when tickets are updated upon workflow completion. Currently implemented for onboarding and offboarding processes, with flexibility to be reused as a sub-workflow or completion handler for future automations.</t>
+  </si>
+  <si>
+    <t>Smart Asset Billing Audit</t>
+  </si>
+  <si>
+    <t>Automates post-ticket validation in HaloPSA by analyzing closed Incident and Service Request tickets with AI to identify unbilled assets, and sends email alerts to Jason and Ashley when discrepancies are detected.</t>
+  </si>
+  <si>
+    <t>AI First Response to HaloPSA tickets</t>
+  </si>
+  <si>
+    <t>MS365, OpenAI, HaloPSA, Rewst</t>
+  </si>
+  <si>
+    <t>OpenAI, HaloPSA, MS365, Rewst</t>
+  </si>
+  <si>
+    <t>Builds an automation that sends immediate acknowledgements for new email-generated tickets, including the ticket ID to improve user communication and ensure SLA compliance, with future plans to add Microsoft Teams notifications.</t>
   </si>
 </sst>
 </file>
@@ -165,13 +180,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -507,7 +525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D3FE286-6749-4234-BE82-DEFA19428F78}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27" style="2" bestFit="1" customWidth="1"/>
@@ -539,7 +557,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>6</v>
@@ -553,7 +571,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>9</v>
@@ -567,7 +585,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>6</v>
@@ -581,7 +599,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>6</v>
@@ -592,10 +610,10 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>6</v>
@@ -606,10 +624,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>6</v>
@@ -617,16 +635,44 @@
     </row>
     <row r="8" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -639,6 +685,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010037CFE03F1E3D084DA4C7DCDB2F33373B" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="48fbfec5ba6da941d58a6bba8473d12a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="9cb81d7b-fefe-42a9-a0f2-5871603dfeb9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0e0a672e89e325df77fa989dac01fde5" ns3:_="">
     <xsd:import namespace="9cb81d7b-fefe-42a9-a0f2-5871603dfeb9"/>
@@ -788,15 +843,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -806,6 +852,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8188391C-85BF-4856-861E-1F470AB9C963}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B78AE0C9-394B-4984-AE8D-B785F12488C7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -823,14 +877,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8188391C-85BF-4856-861E-1F470AB9C963}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F975563D-C219-4A29-B1CB-37D50519E395}">
   <ds:schemaRefs>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://continuousnet-my.sharepoint.com/personal/satyam_continuous_net/Documents/Desktop/Project Tracker Dashboard/project-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{C4665E14-9296-465B-A7EF-B8144438D411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E801EA7F-8186-4A6D-8878-10ED36AC1666}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{C4665E14-9296-465B-A7EF-B8144438D411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4A66F11-1071-4CDF-A318-6D7F1D90D9F3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B5181292-B819-4253-93D6-A2C77ED0862A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
   <si>
     <t xml:space="preserve">Project Name </t>
   </si>
@@ -132,6 +132,24 @@
   </si>
   <si>
     <t>Builds an automation that sends immediate acknowledgements for new email-generated tickets, including the ticket ID to improve user communication and ensure SLA compliance, with future plans to add Microsoft Teams notifications.</t>
+  </si>
+  <si>
+    <t>AI Voice Agent</t>
+  </si>
+  <si>
+    <t>MS365, OpenAI, HaloPSA, Twilio</t>
+  </si>
+  <si>
+    <t>Client Face Dashboard</t>
+  </si>
+  <si>
+    <t>MS365, Ninja RMM, HaloPSA, Rewst</t>
+  </si>
+  <si>
+    <t>This project focuses on developing a dashboard that can be used by multiple clients to visualize key data. It will display insights from surveys and CSAT scores, along with service-related information such as ticket status (open, closed, categorized) and device health metrics. The dashboard will also track total workstations and patch compliance, with the ability to filter data by location and other relevant parameters.</t>
+  </si>
+  <si>
+    <t>This project involves developing a voice agent that operates after business hours to handle user calls. The agent will receive incoming calls, understand and capture the user’s issue, and either route the call to an available on-call engineer or schedule a callback if no engineer is available at that time.</t>
   </si>
 </sst>
 </file>
@@ -525,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D3FE286-6749-4234-BE82-DEFA19428F78}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27" style="2" bestFit="1" customWidth="1"/>
@@ -672,6 +690,34 @@
         <v>31</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -685,12 +731,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="9cb81d7b-fefe-42a9-a0f2-5871603dfeb9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -844,17 +889,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="9cb81d7b-fefe-42a9-a0f2-5871603dfeb9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8188391C-85BF-4856-861E-1F470AB9C963}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F975563D-C219-4A29-B1CB-37D50519E395}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="9cb81d7b-fefe-42a9-a0f2-5871603dfeb9"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -878,17 +932,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F975563D-C219-4A29-B1CB-37D50519E395}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8188391C-85BF-4856-861E-1F470AB9C963}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="9cb81d7b-fefe-42a9-a0f2-5871603dfeb9"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://continuousnet-my.sharepoint.com/personal/satyam_continuous_net/Documents/Desktop/Project Tracker Dashboard/project-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{C4665E14-9296-465B-A7EF-B8144438D411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4A66F11-1071-4CDF-A318-6D7F1D90D9F3}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:1_{C4665E14-9296-465B-A7EF-B8144438D411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9EFF405-8F80-4267-B0D4-60F8ACC92788}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B5181292-B819-4253-93D6-A2C77ED0862A}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B5181292-B819-4253-93D6-A2C77ED0862A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="41">
   <si>
     <t xml:space="preserve">Project Name </t>
   </si>
@@ -150,6 +150,15 @@
   </si>
   <si>
     <t>This project involves developing a voice agent that operates after business hours to handle user calls. The agent will receive incoming calls, understand and capture the user’s issue, and either route the call to an available on-call engineer or schedule a callback if no engineer is available at that time.</t>
+  </si>
+  <si>
+    <t>Client-Facing HIPAA Compliance Chatbot</t>
+  </si>
+  <si>
+    <t>Develop a client-facing chatbot that enables users to assess their HIPAA compliance status through conversational interaction. The chatbot should guide clients through compliance-related questions, identify gaps, and provide actionable recommendations.</t>
+  </si>
+  <si>
+    <t>OpenAI, HaloPSA, MS365, Python, Docker</t>
   </si>
 </sst>
 </file>
@@ -543,7 +552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D3FE286-6749-4234-BE82-DEFA19428F78}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27" style="2" bestFit="1" customWidth="1"/>
@@ -693,7 +702,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>32</v>
       </c>
@@ -718,6 +727,20 @@
         <v>36</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -731,11 +754,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="9cb81d7b-fefe-42a9-a0f2-5871603dfeb9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -889,26 +913,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="9cb81d7b-fefe-42a9-a0f2-5871603dfeb9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F975563D-C219-4A29-B1CB-37D50519E395}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8188391C-85BF-4856-861E-1F470AB9C963}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="9cb81d7b-fefe-42a9-a0f2-5871603dfeb9"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -932,9 +947,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8188391C-85BF-4856-861E-1F470AB9C963}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F975563D-C219-4A29-B1CB-37D50519E395}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="9cb81d7b-fefe-42a9-a0f2-5871603dfeb9"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:1_{C4665E14-9296-465B-A7EF-B8144438D411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9EFF405-8F80-4267-B0D4-60F8ACC92788}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B5181292-B819-4253-93D6-A2C77ED0862A}"/>
+    <workbookView xWindow="28665" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{B5181292-B819-4253-93D6-A2C77ED0862A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://continuousnet-my.sharepoint.com/personal/satyam_continuous_net/Documents/Desktop/Project Tracker Dashboard/project-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:1_{C4665E14-9296-465B-A7EF-B8144438D411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9EFF405-8F80-4267-B0D4-60F8ACC92788}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="13_ncr:1_{C4665E14-9296-465B-A7EF-B8144438D411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C855E608-3E20-4C60-8F89-F0E413187E14}"/>
   <bookViews>
-    <workbookView xWindow="28665" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{B5181292-B819-4253-93D6-A2C77ED0862A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B5181292-B819-4253-93D6-A2C77ED0862A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="45">
   <si>
     <t xml:space="preserve">Project Name </t>
   </si>
@@ -159,6 +159,18 @@
   </si>
   <si>
     <t>OpenAI, HaloPSA, MS365, Python, Docker</t>
+  </si>
+  <si>
+    <t>On hold</t>
+  </si>
+  <si>
+    <t>CI/CD pipelines for DevOps Projects</t>
+  </si>
+  <si>
+    <t>Set up multi-environment CI/CD pipeline (dev/staging/prod) for the Eva Voice Agent. Each environment runs in isolated Docker containers on a single LXC, auto-deployed via a self-hosted GitHub Actions runner on push to the respective branch.</t>
+  </si>
+  <si>
+    <t>GitHub Actions, Docker, NGINX Proxy Manager, Technitium DNS, Proxmox LXC</t>
   </si>
 </sst>
 </file>
@@ -233,6 +245,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -552,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D3FE286-6749-4234-BE82-DEFA19428F78}">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27" style="2" bestFit="1" customWidth="1"/>
@@ -727,7 +743,7 @@
         <v>36</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
@@ -741,6 +757,20 @@
         <v>39</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -754,12 +784,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="9cb81d7b-fefe-42a9-a0f2-5871603dfeb9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -913,17 +942,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="9cb81d7b-fefe-42a9-a0f2-5871603dfeb9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8188391C-85BF-4856-861E-1F470AB9C963}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F975563D-C219-4A29-B1CB-37D50519E395}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="9cb81d7b-fefe-42a9-a0f2-5871603dfeb9"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -947,17 +985,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F975563D-C219-4A29-B1CB-37D50519E395}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8188391C-85BF-4856-861E-1F470AB9C963}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="9cb81d7b-fefe-42a9-a0f2-5871603dfeb9"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://continuousnet-my.sharepoint.com/personal/satyam_continuous_net/Documents/Desktop/Project Tracker Dashboard/project-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="13_ncr:1_{C4665E14-9296-465B-A7EF-B8144438D411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C855E608-3E20-4C60-8F89-F0E413187E14}"/>
+  <xr:revisionPtr revIDLastSave="76" documentId="13_ncr:1_{C4665E14-9296-465B-A7EF-B8144438D411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BBE08D0-5C10-4DF1-8143-D28A00950DFA}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B5181292-B819-4253-93D6-A2C77ED0862A}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B5181292-B819-4253-93D6-A2C77ED0862A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="48">
   <si>
     <t xml:space="preserve">Project Name </t>
   </si>
@@ -161,9 +161,6 @@
     <t>OpenAI, HaloPSA, MS365, Python, Docker</t>
   </si>
   <si>
-    <t>On hold</t>
-  </si>
-  <si>
     <t>CI/CD pipelines for DevOps Projects</t>
   </si>
   <si>
@@ -171,6 +168,18 @@
   </si>
   <si>
     <t>GitHub Actions, Docker, NGINX Proxy Manager, Technitium DNS, Proxmox LXC</t>
+  </si>
+  <si>
+    <t>Cancelled</t>
+  </si>
+  <si>
+    <t>CPC</t>
+  </si>
+  <si>
+    <t>Python, FastAPI, PostgreSQL, MS365, MCP HaloPSA, Docker LXC, Github</t>
+  </si>
+  <si>
+    <t>Continuous Networks' internal product and pricing catalog, replacing spreadsheets and Zomentum for products, bundles, packages, pricing tiers, discount rules, and vendor management. Exposes an AI-queryable interface via MCP, and syncs one-way into HaloPSA so recurring pricing and asset-group categorization stay accurate instead of every item showing up as a one-time sale in the wrong group</t>
   </si>
 </sst>
 </file>
@@ -245,10 +254,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -568,7 +573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D3FE286-6749-4234-BE82-DEFA19428F78}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27" style="2" bestFit="1" customWidth="1"/>
@@ -729,7 +734,7 @@
         <v>37</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
@@ -743,7 +748,7 @@
         <v>36</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
@@ -757,20 +762,34 @@
         <v>39</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="D14" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -784,14 +803,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="9cb81d7b-fefe-42a9-a0f2-5871603dfeb9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010037CFE03F1E3D084DA4C7DCDB2F33373B" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="48fbfec5ba6da941d58a6bba8473d12a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="9cb81d7b-fefe-42a9-a0f2-5871603dfeb9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0e0a672e89e325df77fa989dac01fde5" ns3:_="">
     <xsd:import namespace="9cb81d7b-fefe-42a9-a0f2-5871603dfeb9"/>
@@ -941,6 +952,14 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="9cb81d7b-fefe-42a9-a0f2-5871603dfeb9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -951,22 +970,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F975563D-C219-4A29-B1CB-37D50519E395}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="9cb81d7b-fefe-42a9-a0f2-5871603dfeb9"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B78AE0C9-394B-4984-AE8D-B785F12488C7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -984,6 +987,22 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F975563D-C219-4A29-B1CB-37D50519E395}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="9cb81d7b-fefe-42a9-a0f2-5871603dfeb9"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8188391C-85BF-4856-861E-1F470AB9C963}">
   <ds:schemaRefs>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://continuousnet-my.sharepoint.com/personal/satyam_continuous_net/Documents/Desktop/Project Tracker Dashboard/project-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="13_ncr:1_{C4665E14-9296-465B-A7EF-B8144438D411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BBE08D0-5C10-4DF1-8143-D28A00950DFA}"/>
+  <xr:revisionPtr revIDLastSave="83" documentId="13_ncr:1_{C4665E14-9296-465B-A7EF-B8144438D411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F88C4BC-B62E-4F1C-B674-996B3C3380E3}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B5181292-B819-4253-93D6-A2C77ED0862A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="51">
   <si>
     <t xml:space="preserve">Project Name </t>
   </si>
@@ -180,6 +180,15 @@
   </si>
   <si>
     <t>Continuous Networks' internal product and pricing catalog, replacing spreadsheets and Zomentum for products, bundles, packages, pricing tiers, discount rules, and vendor management. Exposes an AI-queryable interface via MCP, and syncs one-way into HaloPSA so recurring pricing and asset-group categorization stay accurate instead of every item showing up as a one-time sale in the wrong group</t>
+  </si>
+  <si>
+    <t>CPC Quote &amp; Pricing Tool</t>
+  </si>
+  <si>
+    <t>Python, MS365, MCP HaloPSA, Github</t>
+  </si>
+  <si>
+    <t>Internal quoting and pricing tool for configuring server solutions, automatically calculating totals based on defined pricing, supporting pricing overrides, and generating quotes tied to opportunities in CPC/Zomentum</t>
   </si>
 </sst>
 </file>
@@ -254,6 +263,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -573,7 +586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D3FE286-6749-4234-BE82-DEFA19428F78}">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27" style="2" bestFit="1" customWidth="1"/>
@@ -776,7 +789,7 @@
         <v>42</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="72" x14ac:dyDescent="0.3">
@@ -790,6 +803,20 @@
         <v>47</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -803,6 +830,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="9cb81d7b-fefe-42a9-a0f2-5871603dfeb9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010037CFE03F1E3D084DA4C7DCDB2F33373B" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="48fbfec5ba6da941d58a6bba8473d12a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="9cb81d7b-fefe-42a9-a0f2-5871603dfeb9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0e0a672e89e325df77fa989dac01fde5" ns3:_="">
     <xsd:import namespace="9cb81d7b-fefe-42a9-a0f2-5871603dfeb9"/>
@@ -952,24 +996,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="9cb81d7b-fefe-42a9-a0f2-5871603dfeb9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8188391C-85BF-4856-861E-1F470AB9C963}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F975563D-C219-4A29-B1CB-37D50519E395}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="9cb81d7b-fefe-42a9-a0f2-5871603dfeb9"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B78AE0C9-394B-4984-AE8D-B785F12488C7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -985,28 +1036,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F975563D-C219-4A29-B1CB-37D50519E395}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="9cb81d7b-fefe-42a9-a0f2-5871603dfeb9"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8188391C-85BF-4856-861E-1F470AB9C963}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>